--- a/default_input.xlsx
+++ b/default_input.xlsx
@@ -23966,7 +23966,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="21" t="n">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="F5" s="23" t="n">
         <v>86.5</v>
